--- a/eda/ket_qua/ket_qua_modelLogisticRegression.xlsx
+++ b/eda/ket_qua/ket_qua_modelLogisticRegression.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion Matrix" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KFold" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,113 +456,26 @@
         <v>0.7651292802236197</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>132</v>
-      </c>
-      <c r="B2" t="n">
-        <v>18</v>
-      </c>
-    </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>39</v>
+        <v>0.7839506172839507</v>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KFold Scores</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>0.7592592592592593</v>
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.7729909154437455</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7547169811320755</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>0.7169811320754716</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>0.7547169811320755</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>0.7547169811320755</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>0.7924528301886793</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>0.7735849056603774</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>0.8113207547169812</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.75</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.7510917030567685</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7651292802236197</v>
       </c>
     </row>
   </sheetData>

--- a/eda/ket_qua/ket_qua_modelLogisticRegression.xlsx
+++ b/eda/ket_qua/ket_qua_modelLogisticRegression.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,28 @@
         <v>0.7651292802236197</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0.7839506172839507</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.7729909154437455</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7510917030567685</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.7651292802236197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
